--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>55</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>30/07 23:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>30/07 16:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>110</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>09/08 00:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>45</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>50</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>04/08 01:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>45</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>60</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>30/07 16:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F12" t="n">
+        <v>2.35</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>30/07 18:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>40</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F16" t="n">
+        <v>2.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>08/08 00:15</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>45</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>30/07 16:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>23</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>30/07 02:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>45</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
+      <c r="F22" t="n">
+        <v>1.58</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>30/07 12:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F24" t="n">
+        <v>2.7</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,97 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45868.08357125925</v>
+        <v>45868.08357126157</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Tigres – C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tigres – Club PueblaLiga MX</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>09/08 03:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+9,48%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45868.15825478541</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Moins que 31.51re période | Sénégal (F</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sénégal (F) – Rwanda (F)International - Championnat d'Afrique (F)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Moins que 31.51re période</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>30/07 18:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+1,88%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45868.15825478541</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,10 +1494,8 @@
           <t>09/08 03:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1510,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45868.15825478541</v>
+        <v>45868.15825478009</v>
       </c>
     </row>
     <row r="26">
@@ -1539,10 +1537,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2.3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1555,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45868.15825478541</v>
+        <v>45868.15825478009</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ludogorets – HNK RijekaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>30/07 17:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+4,85%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45868.20010329629</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>30/07 17:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,52 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45868.20010329629</v>
+        <v>45868.20010329861</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Basketball | Moins que 62.51re mi-temps | Mozambique</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mozambique F. – Guinée F.International - FIBA Afrique F.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Moins que 62.51re mi-temps</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>30/07 12:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+8,05%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45868.23003366291</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>30/07 12:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.28</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,142 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45868.23003366291</v>
+        <v>45868.2300336574</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Plus que 31.51re période | Cameroun (</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cameroun (F) – Angola (F)International - Championnat d'Afrique (F)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 31.51re période</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>30/07 21:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>49,5%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+8,99%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45868.27641023519</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Beach volley | 21-21er set | Sinisalo/L</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sinisalo/Lahti (FIN) – Álvarez/Moreno (ESP)Europe - EuroBeachVolley (F)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21-21er set</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>30/07 09:40</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+0,55%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45868.27641023519</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Minnesota </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Minnesota United FC – Queretaro FCLeagues Cup</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>31/07 00:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+0,22%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45868.27641023519</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45868.27641023519</v>
+        <v>45868.27641023148</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>30/07 09:40</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
+      <c r="F30" t="n">
+        <v>1.44</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45868.27641023519</v>
+        <v>45868.27641023148</v>
       </c>
     </row>
     <row r="31">
@@ -1756,23 +1752,201 @@
           <t>31/07 00:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+0,22%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45868.27641023148</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Yunchaoket</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yunchaokete Bu – Lorenzo SonegoATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>30/07 16:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>36,0%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45868.31068243403</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Beach volley | 21-2 | Sinisalo/L</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sinisalo/Lahti (FIN) – Álvarez/Moreno (ESP)Europe - EuroBeachVolley (F)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>30/07 09:40</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>75,9%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+1,66%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45868.31068243403</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 4.51er set1er participant | Alejandro </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Alejandro Davidovich Fokina – Corentin MoutetATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>30/07 18:50</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>28,2%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+1,43%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45868.31068243403</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira – Once CaldasPrimera A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>+0,22%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>45868.27641023519</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+0,71%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45868.31068243403</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>30/07 16:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45868.31068243403</v>
+        <v>45868.31068243056</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>30/07 09:40</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
+      <c r="F33" t="n">
+        <v>1.34</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45868.31068243403</v>
+        <v>45868.31068243056</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>30/07 18:50</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F34" t="n">
+        <v>3.6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45868.31068243403</v>
+        <v>45868.31068243056</v>
       </c>
     </row>
     <row r="35">
@@ -1930,10 +1924,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>40</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1946,7 +1938,187 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45868.31068243403</v>
+        <v>45868.31068243056</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | A.Vukic – </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A.Vukic – C.NorrieATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>30/07 16:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+85,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45868.35639426536</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Flavio Cob</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli – Alexis GalarneauATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>30/07 16:10</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+51,9%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45868.35639426536</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | H 1 (−1.5) | Hanyu Guo </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hanyu Guo – Iga SwiatekWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>30/07 16:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+2,45%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45868.35639426536</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Plus que 32.51re période | Mozambique</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mozambique (F) – Republique de Guinée (F)International - Championnat d'Afrique (F)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 32.51re période</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>30/07 12:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+2,06%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45868.35639426536</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>30/07 16:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="F36" t="n">
+        <v>5.5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45868.35639426536</v>
+        <v>45868.35639427084</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>30/07 16:10</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>7</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45868.35639426536</v>
+        <v>45868.35639427084</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>30/07 16:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>45</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45868.35639426536</v>
+        <v>45868.35639427084</v>
       </c>
     </row>
     <row r="39">
@@ -2102,23 +2096,381 @@
           <t>30/07 12:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+2,06%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45868.35639427084</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Fils – P</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A.Fils – P.CarrenoBustaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>30/07 20:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45868.39684364295</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | M.Mcdonald</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M.Mcdonald – J.LeheckaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>30/07 18:50</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>25,1%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+50,3%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45868.39684364295</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | H.Guo – I.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>H.Guo – I.SwiatekWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>30/07 16:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>46,8%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+40,3%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45868.39684364295</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | B.Nakashim</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B.Nakashima – E.QuinnATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>30/07 17:40</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>31,2%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+17,0%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45868.39684364295</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | B.Bencic –</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B.Bencic – E.BouchardWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>30/07 23:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>70,5%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+12,8%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45868.39684364295</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | S.Tsitsipa</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>S.Tsitsipas – C.O'ConnellATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>30/07 21:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>+2,06%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>45868.35639426536</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+11,9%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45868.39684364295</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | Y.Starodub</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Y.Starodubtsev – M.FrechWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>30/07 18:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+6,23%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45868.39684364295</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | R.Zarazua </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>R.Zarazua – J.OstapenkoWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>30/07 16:10</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>89,1%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+2,47%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45868.39684364295</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>30/07 20:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>30/07 18:50</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>6</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>30/07 16:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>30/07 17:40</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="F43" t="n">
+        <v>3.75</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
       </c>
     </row>
     <row r="44">
@@ -2319,10 +2311,8 @@
           <t>30/07 23:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F44" t="n">
+        <v>1.6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2335,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
       </c>
     </row>
     <row r="45">
@@ -2364,10 +2354,8 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.25</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2380,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
       </c>
     </row>
     <row r="46">
@@ -2409,10 +2397,8 @@
           <t>30/07 18:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2425,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
       </c>
     </row>
     <row r="47">
@@ -2454,10 +2440,8 @@
           <t>30/07 16:10</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
+      <c r="F47" t="n">
+        <v>1.15</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2470,7 +2454,187 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45868.39684364295</v>
+        <v>45868.39684364583</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Arthur Fil</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Arthur Fils – Pablo Carreno-BustaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>30/07 20:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+51,1%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45868.43536814044</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Stefanos T</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas – Christopher O'ConnellATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>30/07 21:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+24,4%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45868.43536814044</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Frances Ti</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe – Yosuke WatanukiATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>30/07 17:20</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>22,1%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+10,7%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45868.43536814044</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Plus que 65.51re mi-temps | Cameroun (</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cameroun (F) – Angola (F)International - Championnat d'Afrique (F)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 65.51re mi-temps</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>30/07 21:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>48,3%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+6,35%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45868.43536814044</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>30/07 20:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45868.43536814044</v>
+        <v>45868.43536813658</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.5</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45868.43536814044</v>
+        <v>45868.43536813658</v>
       </c>
     </row>
     <row r="50">
@@ -2573,10 +2569,8 @@
           <t>30/07 17:20</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2589,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45868.43536814044</v>
+        <v>45868.43536813658</v>
       </c>
     </row>
     <row r="51">
@@ -2618,23 +2612,66 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>48,3%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+6,35%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45868.43536813658</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1 | Fortuna Du</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fortuna Dusseldorf – Hanovre 96Allemagne - 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>09/08 11:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>48,3%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>+6,35%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>45868.43536814044</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>46,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,93%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45868.47344553364</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>09/08 11:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,187 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45868.47344553364</v>
+        <v>45868.47344553241</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Malmo FF –</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Malmo FF – Rigas Futbola SkolaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+34,4%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45868.535882631</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Corinthians – FortalezaSérie A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+23,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45868.535882631</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | X | Fomget Gen</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fomget Genclick Ve Spor – Neftchi Baku PFCLigue des Champions (F) A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>30/07 16:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45868.535882631</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 4.5 - aces1er participant | Tristan Bo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tristan Boyer – Jakub MensikATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - aces1er participant</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>30/07 17:40</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>47,6%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+7,00%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45868.535882631</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>60</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45868.535882631</v>
+        <v>45868.53588262732</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>60</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45868.535882631</v>
+        <v>45868.53588262732</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>30/07 16:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>55</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45868.535882631</v>
+        <v>45868.53588262732</v>
       </c>
     </row>
     <row r="56">
@@ -2833,10 +2827,8 @@
           <t>30/07 17:40</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.25</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2849,7 +2841,187 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45868.535882631</v>
+        <v>45868.53588262732</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | X | Fomget Gen</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fomget Genclick Ve Spor F. – Baku F.Europe - Ligue des Champions F.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>30/07 16:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>64.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+25,7%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45868.57110850976</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | C.McNally </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C.McNally – R.SramkovaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>30/07 16:10</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>71,8%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+7,70%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45868.57110850976</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | Racing Uni</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Racing Union Luxembourg (F) – AEK Athens (F)International. Ligue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+7,45%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45868.57110850976</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | X - aces | M.Joint – </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>M.Joint – M.KesslerWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>30/07 15:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+7,08%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45868.57110850976</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>30/07 16:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>64.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>64</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45868.57110850976</v>
+        <v>45868.57110850694</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>30/07 16:10</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F58" t="n">
+        <v>1.5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45868.57110850976</v>
+        <v>45868.57110850694</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
+      <c r="F59" t="n">
+        <v>5.9</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45868.57110850976</v>
+        <v>45868.57110850694</v>
       </c>
     </row>
     <row r="60">
@@ -3005,10 +2999,8 @@
           <t>30/07 15:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.75</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3021,7 +3013,52 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45868.57110850976</v>
+        <v>45868.57110850694</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Plus que 5.51er set1er participant | Francisco </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Francisco Comesana – Alex De MinaurATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>30/07 22:10</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>31,7%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+10,9%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45868.5994844053</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>30/07 22:10</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,142 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45868.5994844053</v>
+        <v>45868.59948440972</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 5.51er set1er participant | Tristan Bo</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tristan Boyer – Jakub MensikATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>30/07 17:40</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+8,68%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45868.64375573923</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – NK CeljeLigue Europa</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>31/07 16:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+7,26%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45868.64375573923</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Spartak Tr</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Spartak Trnava – Paola HiberniansEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>31/07 15:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+6,42%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45868.64375573923</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>30/07 17:40</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F62" t="n">
+        <v>2.7</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45868.64375573923</v>
+        <v>45868.64375574074</v>
       </c>
     </row>
     <row r="63">
@@ -3130,10 +3128,8 @@
           <t>31/07 16:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>45</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3146,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45868.64375573923</v>
+        <v>45868.64375574074</v>
       </c>
     </row>
     <row r="64">
@@ -3175,10 +3171,8 @@
           <t>31/07 15:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>12</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3191,7 +3185,142 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45868.64375573923</v>
+        <v>45868.64375574074</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | The New Sa</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>The New Saints – Briton FerryCymru Premier</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>08/08 18:45</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+24,8%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45868.68756200325</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ludogorets Razgrad – RijekaEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>30/07 17:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45868.68756200325</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 2.5 - break1er participant | Frances Ti</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe – Yosuke WatanukiATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Moins que 2.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>30/07 17:40</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+6,98%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45868.68756200325</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>08/08 18:45</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>45</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45868.68756200325</v>
+        <v>45868.68756200231</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>30/07 17:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
+      <c r="F66" t="n">
+        <v>2.62</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45868.68756200325</v>
+        <v>45868.68756200231</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>30/07 17:40</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F67" t="n">
+        <v>2.15</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,52 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45868.68756200325</v>
+        <v>45868.68756200231</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 11.5 - tirs2e équipe | Breidablik</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Breidablik Kopavogur – Lech PoznanEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>30/07 18:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+5,94%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45868.7245782822</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,10 +3343,8 @@
           <t>30/07 18:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F68" t="n">
+        <v>2.4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,142 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45868.7245782822</v>
+        <v>45868.72457828704</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | T.Etchever</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>T.Etcheverry – F.CerundoloATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31/07 16:10</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>53,2%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+22,3%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45868.77436356582</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fenerbahce – AlanyasporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>09/08 18:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+17,6%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45868.77436356582</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | San Martin</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>San Martin de San Juan – CA SarmientoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>09/08 17:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45868.77436356582</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>31/07 16:10</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F69" t="n">
+        <v>2.3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45868.77436356582</v>
+        <v>45868.77436356481</v>
       </c>
     </row>
     <row r="70">
@@ -3431,10 +3429,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>50</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3447,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45868.77436356582</v>
+        <v>45868.77436356481</v>
       </c>
     </row>
     <row r="71">
@@ -3476,23 +3472,156 @@
           <t>09/08 17:30</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="n">
+        <v>45</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45868.77436356481</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Metaloglob</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Metaloglobus Bucuresti – Dinamo BucarestLiga 1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>08/08 18:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+65,2%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45868.80629417399</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Lokomotiva</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb – HNK Vukovar 1991HNL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>01/08 18:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>+14,0%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>45868.77436356582</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+4,99%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45868.80629417399</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | H 1 (−1.5) | Alexander </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Alexander Zverev – Matteo ArnaldiATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>31/07 23:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>73,6%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+4,49%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45868.80629417399</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>60</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45868.80629417399</v>
+        <v>45868.80629417824</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>45</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45868.80629417399</v>
+        <v>45868.80629417824</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>31/07 23:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="F74" t="n">
+        <v>1.42</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,97 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45868.80629417399</v>
+        <v>45868.80629417824</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | Plus que 0.5 - tie-break | F.Tiafoe –</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>F.Tiafoe – Y.WatanukiATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 0.5 - tie-break</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>30/07 20:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>48,9%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+7,58%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45868.8508645658</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball | Plus que 32.51re période | Cameroun (</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cameroun (F) – Angola (F)International - Afrobasket (F)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 32.51re période</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>30/07 21:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+4,16%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45868.8508645658</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,10 +3644,8 @@
           <t>30/07 20:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F75" t="n">
+        <v>2.2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45868.8508645658</v>
+        <v>45868.85086456018</v>
       </c>
     </row>
     <row r="76">
@@ -3689,10 +3687,8 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F76" t="n">
+        <v>2.15</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3705,7 +3701,97 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45868.8508645658</v>
+        <v>45868.85086456018</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Hajduk Spl</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Hajduk Split – Istra 1961HNL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45868.89090012317</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis | Tie-break: Oui | Karen Khac</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Karen Khachanov – Emilio NavaToronto ATP</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>31/07 15:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+4,54%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45868.89090012317</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,10 +3730,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>55</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45868.89090012317</v>
+        <v>45868.89090012731</v>
       </c>
     </row>
     <row r="78">
@@ -3775,10 +3773,8 @@
           <t>31/07 15:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F78" t="n">
+        <v>2.5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3791,7 +3787,97 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45868.89090012317</v>
+        <v>45868.89090012731</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 5.51er set2e participant | Francisco </t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Francisco Comesana – Alex De MinaurATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>30/07 23:55</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+6,22%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45868.9329235217</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Tie-break: Oui | Daniil Med</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev – Alexei PopyrinATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>01/08 00:10</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+5,16%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45868.9329235217</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-30.xlsx
+++ b/data/valuebets_database_2025-07-30.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3816,10 +3816,8 @@
           <t>30/07 23:55</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>7.75</t>
-        </is>
+      <c r="F79" t="n">
+        <v>7.75</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3832,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45868.9329235217</v>
+        <v>45868.93292351852</v>
       </c>
     </row>
     <row r="80">
@@ -3861,10 +3859,8 @@
           <t>01/08 00:10</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F80" t="n">
+        <v>2.45</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3877,7 +3873,97 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45868.9329235217</v>
+        <v>45868.93292351852</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Slovack</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>FC Slovacko – Slavia PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>03/08 13:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+29,2%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45868.97472445199</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball | Plus que 32.51re période | Mali (F) –</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mali (F) – Mozambique (F)385076e7 International - Afrobasket (F)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Plus que 32.51re période</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>31/07 15:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>43,2%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+1,45%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45868.97472445199</v>
       </c>
     </row>
   </sheetData>
